--- a/data/trans_bre/P38A-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,65</t>
+          <t>1,3; 5,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,7</t>
+          <t>2,49; 7,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 7,13</t>
+          <t>0,76; 6,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,33</t>
+          <t>1,4; 6,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,76</t>
+          <t>2,74; 8,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 8,09</t>
+          <t>0,83; 7,95</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,33</t>
+          <t>2,73; 7,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,25</t>
+          <t>4,5; 8,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 37,48</t>
+          <t>2,75; 35,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,19</t>
+          <t>3,37; 9,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,62</t>
+          <t>5,48; 11,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 78,16</t>
+          <t>3,39; 65,61</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,48</t>
+          <t>-4,8; 3,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 8,25</t>
+          <t>-0,63; 7,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 8,08</t>
+          <t>-1,41; 7,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 3,95</t>
+          <t>-5,29; 3,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 10,19</t>
+          <t>-0,72; 9,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 9,69</t>
+          <t>-1,44; 8,39</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,01</t>
+          <t>2,75; 6,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,89</t>
+          <t>4,54; 7,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 29,87</t>
+          <t>3,19; 29,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,16</t>
+          <t>3,18; 7,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,54</t>
+          <t>5,43; 9,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 49,77</t>
+          <t>3,75; 48,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38A-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,71</t>
+          <t>1,19; 5,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,39</t>
+          <t>2,42; 7,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,96</t>
+          <t>2,61; 9,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,43</t>
+          <t>1,29; 6,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,36</t>
+          <t>2,61; 8,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,95</t>
+          <t>2,87; 10,82</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,76</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,23</t>
+          <t>2,53; 7,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,93</t>
+          <t>4,43; 9,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 35,17</t>
+          <t>3,6; 9,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,06</t>
+          <t>3,04; 9,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,26</t>
+          <t>5,4; 11,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 65,61</t>
+          <t>4,41; 11,91</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 3,03</t>
+          <t>-4,71; 3,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,86</t>
+          <t>-0,45; 7,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 7,04</t>
+          <t>-1,66; 5,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 3,46</t>
+          <t>-5,13; 4,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 9,57</t>
+          <t>-0,49; 9,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 8,39</t>
+          <t>-1,75; 5,92</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,59</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,01</t>
+          <t>2,8; 6,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,97</t>
+          <t>4,59; 8,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 29,42</t>
+          <t>3,65; 7,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,16</t>
+          <t>3,24; 7,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,65</t>
+          <t>5,41; 9,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 48,84</t>
+          <t>4,35; 9,33</t>
         </is>
       </c>
     </row>
